--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed2train/score_seed2train.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed2train/score_seed2train.xlsx
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.9983860432292265</v>
+        <v>0.9983860432292266</v>
       </c>
       <c r="E141" t="n">
         <v>0.9894050529747351</v>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.9981007435135061</v>
+        <v>0.998100743513506</v>
       </c>
       <c r="E145" t="n">
         <v>0.9920460314774073</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.9942037781655413</v>
+        <v>0.9942037781655414</v>
       </c>
       <c r="E171" t="n">
         <v>0.9797570850202429</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.9913245946878233</v>
+        <v>0.9913245946878234</v>
       </c>
       <c r="E177" t="n">
         <v>0.9697656840513983</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.999257386860407</v>
+        <v>0.9992573868604069</v>
       </c>
       <c r="E188" t="n">
         <v>0.9926650366748166</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.9997241141619208</v>
+        <v>0.999724114161921</v>
       </c>
       <c r="E213" t="n">
         <v>0.9949470252648737</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.9991958917747104</v>
+        <v>0.9991958917747102</v>
       </c>
       <c r="E236" t="n">
         <v>0.9921760391198045</v>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.9991398467118544</v>
+        <v>0.9991398467118543</v>
       </c>
       <c r="E237" t="n">
         <v>0.9939690301548493</v>
@@ -16241,13 +16241,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr"/>
+      <c r="D452" t="n">
+        <v>0.982898936425446</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0.9625101874490628</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0.9683426443202979</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0.7094133697135061</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.8188976377952756</v>
+      </c>
       <c r="I452" t="n">
-        <v>0</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="453">
@@ -16266,13 +16276,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
+      <c r="D453" t="n">
+        <v>0.9808107531470024</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0.9737571312143439</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0.9824120603015075</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0.7174311926605504</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.8292682926829268</v>
+      </c>
       <c r="I453" t="n">
-        <v>0</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="454">
@@ -16291,13 +16311,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
+      <c r="D454" t="n">
+        <v>0.9849839128714235</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0.9724149602301574</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0.9826923076923076</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0.7684210526315789</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.8624472573839662</v>
+      </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="455">
@@ -16316,13 +16346,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
+      <c r="D455" t="n">
+        <v>0.9781829274980804</v>
+      </c>
+      <c r="E455" t="n">
+        <v>0.953630055847013</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.9578686493184635</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0.7630799605133267</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0.8494505494505494</v>
+      </c>
       <c r="I455" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="456">
@@ -16341,13 +16381,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
+      <c r="D456" t="n">
+        <v>0.9665919753685877</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0.9449991538331359</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.9562982005141388</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0.8028776978417266</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0.872897927258506</v>
+      </c>
       <c r="I456" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="457">
@@ -16366,13 +16416,23 @@
           <t>Pattern</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
+      <c r="D457" t="n">
+        <v>0.9988203682425363</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0.9979691995261466</v>
+      </c>
+      <c r="F457" t="n">
+        <v>1</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0.9259259259259259</v>
+      </c>
       <c r="I457" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="458">
@@ -17126,13 +17186,23 @@
           <t>Layered</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
+      <c r="D479" t="n">
+        <v>0.9931895368380981</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.9729226603486207</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.9733629300776915</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0.8657453109575518</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0.9164054336468129</v>
+      </c>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="480">
@@ -17151,13 +17221,23 @@
           <t>Layered</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
+      <c r="D480" t="n">
+        <v>0.9848343763581744</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0.9587070570316466</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0.969672131147541</v>
+      </c>
+      <c r="G480" t="n">
+        <v>0.8510791366906475</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0.9065134099616858</v>
+      </c>
       <c r="I480" t="n">
-        <v>0</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="481">
